--- a/Exam/gymtrackerpro/lib/controller/__tests__/it/workout-session-controller/deleteWorkoutSession-it-form.xlsx
+++ b/Exam/gymtrackerpro/lib/controller/__tests__/it/workout-session-controller/deleteWorkoutSession-it-form.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="56">
   <si>
     <t>Statement: deleteWorkoutSession(workoutSessionId: string): Promise&lt;ActionResult&lt;void&gt;&gt; — delegates to workoutSessionService.deleteWorkoutSession() and returns a void ActionResult on success.</t>
   </si>
@@ -82,16 +82,17 @@
     <t>1</t>
   </si>
   <si>
-    <t>Member seeded via userService.createMember(). Exercise seeded via exerciseService.createExercise(). Session seeded via workoutSessionService.createWorkoutSession() with that exercise.</t>
-  </si>
-  <si>
-    <t>deleteWorkoutSession(seededSession.id)</t>
+    <t xml:space="preserve">Member seeded via userService.createMember(). Exercise seeded via exerciseService.createExercise(). Session seeded via workoutSessionService.createWorkoutSession() with that exercise.
+const inputId: string = seededSession.id</t>
+  </si>
+  <si>
+    <t>deleteWorkoutSession(inputId)</t>
   </si>
   <si>
     <t>{ success: true, data: undefined }</t>
   </si>
   <si>
-    <t>Row no longer present in workout_sessions or workout_session_exercises tables</t>
+    <t>workout_sessions row and its linked workout_session_exercises row no longer present</t>
   </si>
   <si>
     <t>Passed</t>
@@ -100,10 +101,8 @@
     <t>2</t>
   </si>
   <si>
-    <t>Empty database.</t>
-  </si>
-  <si>
-    <t>deleteWorkoutSession("00000000-0000-0000-0000-000000000000")</t>
+    <t xml:space="preserve">Empty database.
+const inputId: string = "00000000-0000-0000-0000-000000000000"</t>
   </si>
   <si>
     <t>{ success: false, message: defined non-empty string (NotFoundError message) }</t>
@@ -115,13 +114,31 @@
     <t>3</t>
   </si>
   <si>
-    <t>Member seeded via userService.createMember(). Exercise seeded via exerciseService.createExercise(). Two sessions seeded via workoutSessionService.createWorkoutSession(): sessionA ("2024-01-01"), sessionB ("2024-02-01").</t>
-  </si>
-  <si>
-    <t>deleteWorkoutSession(sessionA.id)</t>
+    <t xml:space="preserve">Member seeded via userService.createMember(). Two exercises seeded: benchPressExercise, deadliftExercise. Session seeded via workoutSessionService.createWorkoutSession() with both exercises.
+const inputId: string = seededSession.id</t>
+  </si>
+  <si>
+    <t>workout_sessions row and all linked workout_session_exercises rows (both exercise entries) no longer present</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Member seeded via userService.createMember(). Exercise seeded via exerciseService.createExercise(). Two sessions seeded: sessionA (date = "2024-01-01"), sessionB (date = "2024-02-01").
+const inputId: string = sessionA.id</t>
   </si>
   <si>
     <t>sessionA and its workout_session_exercises rows removed; sessionB rows still present</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Member seeded via userService.createMember(). Exercise seeded via exerciseService.createExercise(). Two sessions seeded: sessionA (date = "2024-01-01"), sessionB (date = "2024-02-01"). Prior call to deleteWorkoutSession() with id "00000000-0000-0000-0000-000000000000" executed and returned { success: false }.
+const inputId: string = sessionB.id</t>
+  </si>
+  <si>
+    <t>sessionB and its workout_session_exercises rows removed; sessionA rows still present</t>
   </si>
   <si>
     <t>Testing</t>
@@ -806,12 +823,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="80" customWidth="1"/>
-    <col min="4" max="4" width="64" customWidth="1"/>
+    <col min="4" max="4" width="33" customWidth="1"/>
     <col min="5" max="6" width="80" customWidth="1"/>
     <col min="7" max="7" width="17" customWidth="1"/>
   </cols>
@@ -839,7 +856,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" ht="65" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -873,13 +890,13 @@
         <v>28</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>26</v>
@@ -890,21 +907,67 @@
         <v>1</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="D4" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" ht="65" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="D5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="6" t="s">
         <v>26</v>
       </c>
     </row>
@@ -933,17 +996,17 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -955,40 +1018,40 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="K5" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="L5" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="J5" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>42</v>
-      </c>
       <c r="M5" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -996,40 +1059,40 @@
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C6" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D6" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
